--- a/Funcn.xlsx
+++ b/Funcn.xlsx
@@ -4,12 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9708" activeTab="2"/>
+    <workbookView windowWidth="23040" windowHeight="9708" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Named ranges" sheetId="1" r:id="rId1"/>
     <sheet name="textfunc" sheetId="2" r:id="rId2"/>
     <sheet name="datefunc" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="Sales">'Named ranges'!$B$4:$B$6</definedName>
@@ -1866,7 +1867,7 @@
       </c>
       <c r="E4" s="1">
         <f ca="1">TODAY()</f>
-        <v>46268</v>
+        <v>46269</v>
       </c>
     </row>
     <row r="5" spans="4:7">
@@ -1875,7 +1876,7 @@
       </c>
       <c r="E5" s="2">
         <f ca="1">NOW()</f>
-        <v>46268.7894791667</v>
+        <v>46269.7757523148</v>
       </c>
     </row>
     <row r="6" spans="4:7">
@@ -1943,4 +1944,15 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>